--- a/results/Int Task Remove ACC 0.2/Rando_3_permute.xlsx
+++ b/results/Int Task Remove ACC 0.2/Rando_3_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6621386276558689</v>
+        <v>0.6596133751306166</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6505224660397074</v>
+        <v>0.6596656217345873</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6535527690700105</v>
+        <v>0.6503308951584814</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6530477185649599</v>
+        <v>0.6479972135144549</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6575931731104145</v>
+        <v>0.6477359804946012</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6560083594566353</v>
+        <v>0.6381400208986416</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6595437129919889</v>
+        <v>0.6386450714036921</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6596656217345873</v>
+        <v>0.6378091257401602</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6684952978056427</v>
+        <v>0.6404388714733542</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6801114594218043</v>
+        <v>0.6379136189481017</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6796064089167537</v>
+        <v>0.6221351445489376</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6874956461163357</v>
+        <v>0.6257227446882619</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6893939393939394</v>
+        <v>0.6252176941832114</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6893242772553118</v>
+        <v>0.6215604319052594</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6808429118773947</v>
+        <v>0.6225182863113897</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6857715081853013</v>
+        <v>0.6230233368164403</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6569836293974225</v>
+        <v>0.607488679902473</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6569836293974225</v>
+        <v>0.6112156043190526</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.657488679902473</v>
+        <v>0.6112156043190526</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6564785788923719</v>
+        <v>0.6134273772204807</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6539533263671194</v>
+        <v>0.630163706025775</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6519331243469174</v>
+        <v>0.6442006269592476</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6540752351097179</v>
+        <v>0.6418669453152213</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6670672239637757</v>
+        <v>0.6420585161964472</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6667537443399513</v>
+        <v>0.6404737025426681</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6677638453500523</v>
+        <v>0.606495994427029</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6561476837338907</v>
+        <v>0.6042319749216301</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6819749216300941</v>
+        <v>0.6034831069313829</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6819749216300941</v>
+        <v>0.6079588993382097</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6768721699756182</v>
+        <v>0.6090038314176245</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6634447927551377</v>
+        <v>0.5968826192964124</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6571926158133055</v>
+        <v>0.5973180076628353</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6527690700104494</v>
+        <v>0.5967432950191571</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6339602925809822</v>
+        <v>0.5967432950191571</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6597352838732149</v>
+        <v>0.5980668756530826</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6597352838732149</v>
+        <v>0.5846917450365726</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6613026819923371</v>
+        <v>0.5850748867990248</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6613026819923371</v>
+        <v>0.5850748867990248</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6548066875653082</v>
+        <v>0.5940438871473355</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.693312434691745</v>
+        <v>0.5541797283176593</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6919191919191918</v>
+        <v>0.5556948798328109</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6919191919191918</v>
+        <v>0.5413444792755138</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6953152211772902</v>
+        <v>0.5436955764541972</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6953152211772902</v>
+        <v>0.5342737722048068</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6501741553465692</v>
+        <v>0.5378091257401603</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6628004179728317</v>
+        <v>0.5261407175200279</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6199756182514803</v>
+        <v>0.4881748519679555</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5782131661442006</v>
+        <v>0.4884360849878091</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5744339951236503</v>
+        <v>0.4985370950888192</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5326192964123999</v>
+        <v>0.5011145942180425</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5326192964123999</v>
+        <v>0.5008011145942181</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5500174155346569</v>
+        <v>0.4971264367816092</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5264019505398816</v>
+        <v>0.4877220480668756</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5144200626959248</v>
+        <v>0.4851619644723093</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5144200626959248</v>
+        <v>0.4888714733542319</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5186520376175549</v>
+        <v>0.4967258794845001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5336990595611285</v>
+        <v>0.5084465343086033</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5445663531870428</v>
+        <v>0.535632183908046</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5241030999651689</v>
+        <v>0.536642284918147</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5067746429815395</v>
+        <v>0.5017067223963776</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5140195053988157</v>
+        <v>0.5015151515151515</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4865203761755486</v>
+        <v>0.5015151515151515</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4831591779867642</v>
+        <v>0.500191570881226</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4575060954371299</v>
+        <v>0.5006966213862766</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4633925461511669</v>
+        <v>0.5007662835249042</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4672239637756879</v>
+        <v>0.5032915360501568</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4518112156043191</v>
+        <v>0.5032915360501568</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4520724486241727</v>
+        <v>0.5032915360501568</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.450400557297109</v>
+        <v>0.5039881574364333</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4490943921978405</v>
+        <v>0.5035527690700105</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4913618948101707</v>
+        <v>0.5072274468826193</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4936781609195403</v>
+        <v>0.5068965517241379</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4981365377917102</v>
+        <v>0.5046847788227099</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4960640891675375</v>
+        <v>0.4994427028909788</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4899164054336468</v>
+        <v>0.4997561825148032</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4667711598746082</v>
+        <v>0.4993730407523511</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4877742946708464</v>
+        <v>0.4993730407523511</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.493730407523511</v>
+        <v>0.4993730407523511</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4940438871473354</v>
+        <v>0.4993730407523511</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4954371299198885</v>
+        <v>0.4993730407523511</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4960292580982236</v>
+        <v>0.4984326018808777</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4957157784743991</v>
+        <v>0.4984326018808777</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4980320445837687</v>
+        <v>0.4984326018808777</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5000870776732845</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5005747126436781</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4997561825148032</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5003831417624521</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5006966213862766</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4996865203761756</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
